--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -14337,7 +14337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14877,6 +14877,66 @@
         </is>
       </c>
       <c r="F18" t="inlineStr">
+        <is>
+          <t>미지급</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>수입 (+)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>기타 영업수입</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>455000</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>넥서스 수입9월 잔액 2.270.000 카스 1.360.000 지출 50% 455.000 수익입금</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>지급완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>지출 (-)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>양공열 식사 90000만원 대리비용30000원</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -15908,7 +15968,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "수입 (+)", "지급상태": "지급완료", "항목": "기타 영업수입", "금액(원)": 455000, "적요": "넥서스 수입9월 잔액 2.270.000 카스 1.360.000 지출 50% 455.000 수익입금"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -14337,7 +14337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14890,53 +14890,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>수입 (+)</t>
+          <t>지출 (-)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>기타 영업수입</t>
+          <t>접대비</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>455000</v>
+        <v>120000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>넥서스 수입9월 잔액 2.270.000 카스 1.360.000 지출 50% 455.000 수익입금</t>
+          <t>양공열 식사 90000만원 대리비용30000원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>지급완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>지출 (-)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>접대비</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>양공열 식사 90000만원 대리비용30000원</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
         <is>
           <t>미지급</t>
         </is>
@@ -15968,7 +15938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "수입 (+)", "지급상태": "지급완료", "항목": "기타 영업수입", "금액(원)": 455000, "적요": "넥서스 수입9월 잔액 2.270.000 카스 1.360.000 지출 50% 455.000 수익입금"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
         </is>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BW260011</t>
+          <t>BW2600111</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -4273,8 +4273,16 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -7487,7 +7495,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T57" t="n">

--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE108"/>
+  <dimension ref="A1:AE105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3049,17 +3049,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BW-2026-024</t>
+          <t>BW-2026-025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BW260003</t>
+          <t>1ZRR43520337824078</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michele Alves 0.4kg </t>
+          <t xml:space="preserve">Izchel Chacon </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>일반화물</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3109,23 +3109,23 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>25×21×9cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>✅ 배송 완료 (Delivered)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3134,19 +3134,15 @@
         </is>
       </c>
       <c r="T22" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="U22" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>la직배송</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -3176,17 +3172,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BW-2026-025</t>
+          <t>BW-2026-027</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1ZRR43520337824078</t>
+          <t>1ZRR43520304908978</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3206,7 +3202,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Izchel Chacon </t>
+          <t xml:space="preserve">Kathy Shelburg </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3226,7 +3222,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>일반화물</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3252,7 +3248,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3304,12 +3300,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BW-2026-026</t>
+          <t>BW-2026-028</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BW260003</t>
+          <t>1ZRR435228163602</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3324,12 +3320,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>아코글로벌(AKO GLOBAL)</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Olga Voloshina</t>
+          <t>Justin Hodak</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3359,23 +3355,23 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>37×37×25cm(1CTN)</t>
+          <t>34×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.035 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -3384,13 +3380,13 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>351000</v>
+        <v>78000</v>
       </c>
       <c r="U24" t="n">
-        <v>235000</v>
+        <v>60000</v>
       </c>
       <c r="V24" t="n">
-        <v>116000</v>
+        <v>18000</v>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
@@ -3427,12 +3423,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BW-2026-027</t>
+          <t>BW-2026-029</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1ZRR43520304908978</t>
+          <t>1ZRR43520325234013</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3452,7 +3448,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kathy Shelburg </t>
+          <t xml:space="preserve">Laura Swann </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3550,12 +3546,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BW-2026-028</t>
+          <t>BW-2026-030</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1ZRR435228163602</t>
+          <t>1ZRR43520329898022</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3575,7 +3571,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Justin Hodak</t>
+          <t>Yordan Fernandez</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3605,19 +3601,19 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>34×21×13cm(1CTN)</t>
+          <t>33×28×16cm(1CTN)</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.015 CBM</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
@@ -3630,13 +3626,13 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>78000</v>
+        <v>195000</v>
       </c>
       <c r="U26" t="n">
+        <v>135000</v>
+      </c>
+      <c r="V26" t="n">
         <v>60000</v>
-      </c>
-      <c r="V26" t="n">
-        <v>18000</v>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
@@ -3673,12 +3669,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BW-2026-029</t>
+          <t>BW-2026-031</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1ZRR43520325234013</t>
+          <t>1ZRR43520332011633</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3698,7 +3694,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laura Swann </t>
+          <t>Kimberly Tapia</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3728,19 +3724,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>45×30×21cm(1CTN)</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.029 CBM</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -3753,13 +3749,13 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>78000</v>
+        <v>234000</v>
       </c>
       <c r="U27" t="n">
-        <v>60000</v>
+        <v>135000</v>
       </c>
       <c r="V27" t="n">
-        <v>18000</v>
+        <v>99000</v>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
@@ -3796,17 +3792,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BW-2026-030</t>
+          <t>BW-2026-033</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1ZRR43520329898022</t>
+          <t xml:space="preserve">DPK365117536147  </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3816,17 +3812,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>맥익스프레스 인터내셔날(주)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Yordan Fernandez</t>
+          <t>河南省洛阳市老城区畔山兰溪2期 ATTN:小郑  tel: 17575006697</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3851,38 +3847,38 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>33×28×16cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.015 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T28" t="n">
-        <v>195000</v>
+        <v>420000</v>
       </c>
       <c r="U28" t="n">
-        <v>135000</v>
+        <v>340000</v>
       </c>
       <c r="V28" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
@@ -3919,17 +3915,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BW-2026-031</t>
+          <t>BW-2026-034</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1ZRR43520332011633</t>
+          <t>BW2600111</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3939,22 +3935,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>리턴의원</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Kimberly Tapia</t>
+          <t>青岛市城阳区春阳路 92号 百富中心 32号楼 807室</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3964,7 +3960,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3974,43 +3970,47 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>45×30×21cm(1CTN)</t>
+          <t>65×61×124cm(1CTN)</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.029 CBM</t>
+          <t>0.492 CBM</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="Q29" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T29" t="n">
-        <v>234000</v>
+        <v>3690000</v>
       </c>
       <c r="U29" t="n">
-        <v>135000</v>
+        <v>1820400</v>
       </c>
       <c r="V29" t="n">
-        <v>99000</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>1869600</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>우든포장비 132,000원 별도 청구</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>정해균</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4023,8 +4023,16 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -4037,22 +4045,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BW-2026-033</t>
+          <t>BW-2026-035</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">DPK365117536147  </t>
+          <t>1ZRR43520338083680</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4062,17 +4070,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>맥익스프레스 인터내셔날(주)</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>河南省洛阳市老城区畔山兰溪2期 ATTN:小郑  tel: 17575006697</t>
+          <t xml:space="preserve">IMS/Andreina Mascobetto </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4092,24 +4100,24 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>5 박스 (CTN)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>41×30×40cm(5CTN)</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.246 CBM</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q30" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -4122,13 +4130,13 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>420000</v>
+        <v>1790000</v>
       </c>
       <c r="U30" t="n">
-        <v>340000</v>
+        <v>1035000</v>
       </c>
       <c r="V30" t="n">
-        <v>80000</v>
+        <v>755000</v>
       </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
@@ -4160,22 +4168,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BW-2026-034</t>
+          <t>BW-2026-036</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BW2600111</t>
+          <t>1ZRR43520330795738</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4185,22 +4193,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>리턴의원</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>青岛市城阳区春阳路 92号 百富中心 32号楼 807室</t>
+          <t>Wilian Ortiz Lima</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4210,7 +4218,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4220,19 +4228,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>65×61×124cm(1CTN)</t>
+          <t>49×47×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.492 CBM</t>
+          <t>0.051 CBM</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="Q31" t="n">
-        <v>82</v>
+        <v>9</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -4245,22 +4253,18 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>3690000</v>
+        <v>425000</v>
       </c>
       <c r="U31" t="n">
-        <v>1820400</v>
+        <v>235000</v>
       </c>
       <c r="V31" t="n">
-        <v>1869600</v>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>우든포장비 132,000원 별도 청구</t>
-        </is>
-      </c>
+        <v>190000</v>
+      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>정해균</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -4273,16 +4277,8 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
@@ -4300,12 +4296,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BW-2026-035</t>
+          <t>BW-2026-037</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1ZRR43520338083680</t>
+          <t>1ZRR43524238391041</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4325,12 +4321,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">IMS/Andreina Mascobetto </t>
+          <t>Trang Phillip</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>주식회사 케이티글로발</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4345,29 +4341,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>5 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>41×30×40cm(5CTN)</t>
+          <t>49×36×46cm(1CTN)</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.246 CBM</t>
+          <t>0.082 CBM</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -4380,13 +4376,13 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>1790000</v>
+        <v>374000</v>
       </c>
       <c r="U32" t="n">
-        <v>1035000</v>
+        <v>241812</v>
       </c>
       <c r="V32" t="n">
-        <v>755000</v>
+        <v>132188</v>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
@@ -4423,12 +4419,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BW-2026-036</t>
+          <t>BW-2026-038</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1ZRR43520330795738</t>
+          <t>1ZRR43524207297989</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4448,12 +4444,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Wilian Ortiz Lima</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>주식회사 케이티글로발</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4468,29 +4464,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>12 박스 (CTN)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>49×47×22cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.051 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>11</v>
+        <v>237</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -4503,13 +4499,13 @@
         </is>
       </c>
       <c r="T33" t="n">
-        <v>425000</v>
+        <v>5214000</v>
       </c>
       <c r="U33" t="n">
-        <v>235000</v>
+        <v>4052098</v>
       </c>
       <c r="V33" t="n">
-        <v>190000</v>
+        <v>1161902</v>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
@@ -4541,17 +4537,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BW-2026-037</t>
+          <t>BW-2026-039</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1ZRR43524238391041</t>
+          <t>1ZRR43520339569305</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4566,17 +4562,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Trang Phillip</t>
+          <t xml:space="preserve">K.her beauty clinic(Avanti plus)  </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>주식회사 케이티글로발</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4591,7 +4587,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4601,19 +4597,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>49×36×46cm(1CTN)</t>
+          <t>40×31×29cm(1CTN)</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.082 CBM</t>
+          <t>0.037 CBM</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -4622,17 +4618,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T34" t="n">
-        <v>374000</v>
+        <v>390000</v>
       </c>
       <c r="U34" t="n">
-        <v>241812</v>
+        <v>260000</v>
       </c>
       <c r="V34" t="n">
-        <v>132188</v>
+        <v>130000</v>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
@@ -4664,17 +4660,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BW-2026-038</t>
+          <t>BW-2026-040</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1ZRR43524207297989</t>
+          <t>1ZRR43520304831381</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4689,17 +4685,17 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER</t>
+          <t>AVANTI</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>주식회사 케이티글로발</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4714,29 +4710,29 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스 필러</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>12 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>40×31×29cm(1CTN)</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.036 CBM</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>237</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="n">
-        <v>237</v>
+        <v>7</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -4745,17 +4741,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T35" t="n">
-        <v>5214000</v>
+        <v>312000</v>
       </c>
       <c r="U35" t="n">
-        <v>4052098</v>
+        <v>185000</v>
       </c>
       <c r="V35" t="n">
-        <v>1161902</v>
+        <v>127000</v>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
@@ -4792,12 +4788,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BW-2026-039</t>
+          <t>BW-2026-041</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1ZRR43520339569305</t>
+          <t>1ZRR43520318249315</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4812,12 +4808,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">K.her beauty clinic(Avanti plus)  </t>
+          <t>Danielle Stout</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4847,19 +4843,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>40×31×29cm(1CTN)</t>
+          <t>23×16×12cm(1CTN)</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.037 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -4872,13 +4868,13 @@
         </is>
       </c>
       <c r="T36" t="n">
-        <v>390000</v>
+        <v>39000</v>
       </c>
       <c r="U36" t="n">
-        <v>260000</v>
+        <v>35000</v>
       </c>
       <c r="V36" t="n">
-        <v>130000</v>
+        <v>4000</v>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
@@ -4915,12 +4911,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BW-2026-040</t>
+          <t>BW-2026-042</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1ZRR43520304831381</t>
+          <t>1ZRR43520317439326</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4935,12 +4931,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AVANTI</t>
+          <t>Ana Ortiz</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4970,19 +4966,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>40×31×29cm(1CTN)</t>
+          <t>26×18×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.036 CBM</t>
+          <t>0.007 CBM</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -4995,13 +4991,13 @@
         </is>
       </c>
       <c r="T37" t="n">
-        <v>312000</v>
+        <v>78000</v>
       </c>
       <c r="U37" t="n">
-        <v>185000</v>
+        <v>60000</v>
       </c>
       <c r="V37" t="n">
-        <v>127000</v>
+        <v>18000</v>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
@@ -5038,12 +5034,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BW-2026-041</t>
+          <t>BW-2026-043</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1ZRR43520318249315</t>
+          <t>1ZRR43520304641336</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5063,7 +5059,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Danielle Stout</t>
+          <t>Zenith Edge</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5093,19 +5089,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>23×16×12cm(1CTN)</t>
+          <t>26×18×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -5118,13 +5114,13 @@
         </is>
       </c>
       <c r="T38" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="U38" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V38" t="n">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
@@ -5161,12 +5157,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BW-2026-042</t>
+          <t>BW-2026-044</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1ZRR43520317439326</t>
+          <t>1ZRR43520314255342</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5186,7 +5182,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Ana Ortiz</t>
+          <t>Jade Hall</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5216,12 +5212,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>26×18×15cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.007 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -5284,12 +5280,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BW-2026-043</t>
+          <t>BW-2026-045</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1ZRR43520304641336</t>
+          <t>1ZRR43520300681354</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5309,7 +5305,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Zenith Edge</t>
+          <t xml:space="preserve">Dayanna Viquez </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5339,19 +5335,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>26×18×15cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -5364,13 +5360,13 @@
         </is>
       </c>
       <c r="T40" t="n">
-        <v>78000</v>
+        <v>39000</v>
       </c>
       <c r="U40" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="V40" t="n">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
@@ -5407,12 +5403,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BW-2026-044</t>
+          <t>BW-2026-046</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1ZRR43520314255342</t>
+          <t>1ZRR43520318319365</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5432,7 +5428,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Jade Hall</t>
+          <t>Zouzou Tang</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5462,19 +5458,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -5487,13 +5483,13 @@
         </is>
       </c>
       <c r="T41" t="n">
-        <v>78000</v>
+        <v>39000</v>
       </c>
       <c r="U41" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="V41" t="n">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
@@ -5530,12 +5526,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BW-2026-045</t>
+          <t>BW-2026-047</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1ZRR43520300681354</t>
+          <t>1ZRR43520301569377</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5555,7 +5551,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dayanna Viquez </t>
+          <t>Breanna Bryant</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5585,19 +5581,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -5610,13 +5606,13 @@
         </is>
       </c>
       <c r="T42" t="n">
-        <v>39000</v>
+        <v>78000</v>
       </c>
       <c r="U42" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V42" t="n">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
@@ -5653,12 +5649,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BW-2026-046</t>
+          <t>BW-2026-049</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1ZRR43520318319365</t>
+          <t>1ZRR43520302505399</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5673,12 +5669,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Zouzou Tang</t>
+          <t>Maria Brenda</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5708,19 +5704,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>49×36×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.039 CBM</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -5729,17 +5725,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T43" t="n">
-        <v>39000</v>
+        <v>326720</v>
       </c>
       <c r="U43" t="n">
-        <v>35000</v>
+        <v>185000</v>
       </c>
       <c r="V43" t="n">
-        <v>4000</v>
+        <v>141720</v>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
@@ -5759,9 +5755,15 @@
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5776,12 +5778,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BW-2026-047</t>
+          <t>BW-2026-050</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1ZRR43520301569377</t>
+          <t>1ZRR43520308991406</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5796,12 +5798,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Breanna Bryant</t>
+          <t>Trang Phillip</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5831,19 +5833,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>55×36×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.038 CBM</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -5852,17 +5854,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T44" t="n">
-        <v>78000</v>
+        <v>326720</v>
       </c>
       <c r="U44" t="n">
-        <v>60000</v>
+        <v>185000</v>
       </c>
       <c r="V44" t="n">
-        <v>18000</v>
+        <v>141720</v>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
@@ -5882,9 +5884,15 @@
       </c>
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
+      <c r="AC44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5899,12 +5907,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BW-2026-049</t>
+          <t>BW-2026-051</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1ZRR43520302505399</t>
+          <t>1ZRR43520302716938</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5924,12 +5932,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Maria Brenda</t>
+          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5944,7 +5952,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5954,7 +5962,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>49×36×22cm(1CTN)</t>
+          <t>49×35×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5963,14 +5971,14 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
+          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5979,13 +5987,13 @@
         </is>
       </c>
       <c r="T45" t="n">
-        <v>326720</v>
+        <v>205560</v>
       </c>
       <c r="U45" t="n">
-        <v>185000</v>
+        <v>169200</v>
       </c>
       <c r="V45" t="n">
-        <v>141720</v>
+        <v>36360</v>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
@@ -6028,12 +6036,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BW-2026-050</t>
+          <t>BW-2026-052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1ZRR43520308991406</t>
+          <t>1ZRR43520318689411</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6053,7 +6061,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Trang Phillip</t>
+          <t>Kristine Evangelista</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -6083,19 +6091,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>55×36×19cm(1CTN)</t>
+          <t>27×19×17cm(1CTN)</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.038 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -6108,13 +6116,13 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>326720</v>
+        <v>111680</v>
       </c>
       <c r="U46" t="n">
-        <v>185000</v>
+        <v>60000</v>
       </c>
       <c r="V46" t="n">
-        <v>141720</v>
+        <v>51680</v>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
@@ -6152,17 +6160,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BW-2026-051</t>
+          <t>BW-2026-053</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1ZRR43520302716938</t>
+          <t>1ZRR43520333795803</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6177,17 +6185,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
+          <t>Olga Voloshina</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6202,7 +6210,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -6212,12 +6220,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>49×35×22cm(1CTN)</t>
+          <t>37×37×25cm(1CTN)</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.039 CBM</t>
+          <t>0.035 CBM</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -6233,17 +6241,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T47" t="n">
-        <v>205560</v>
+        <v>351000</v>
       </c>
       <c r="U47" t="n">
-        <v>169200</v>
+        <v>235000</v>
       </c>
       <c r="V47" t="n">
-        <v>36360</v>
+        <v>116000</v>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
@@ -6263,15 +6271,9 @@
       </c>
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6281,17 +6283,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BW-2026-052</t>
+          <t>BW-2026-055</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1ZRR43520318689411</t>
+          <t>BW260004</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6306,12 +6308,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Kristine Evangelista</t>
+          <t>Armita Azari</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6331,7 +6333,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>보톡스 필러</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -6341,19 +6343,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>27×19×17cm(1CTN)</t>
+          <t>25×20×10cm(1CTN)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -6362,17 +6364,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T48" t="n">
-        <v>111680</v>
+        <v>39840</v>
       </c>
       <c r="U48" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="V48" t="n">
-        <v>51680</v>
+        <v>4840</v>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
@@ -6392,15 +6394,9 @@
       </c>
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6410,17 +6406,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BW-2026-053</t>
+          <t>BW-2026-056</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1ZRR43520333795803</t>
+          <t>BW260005</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6435,12 +6431,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Olga Voloshina</t>
+          <t>Breanna Ross</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6470,23 +6466,23 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>37×37×25cm(1CTN)</t>
+          <t>21×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.035 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>✈ 항공/해상 선적 완료 (운송 중)</t>
+          <t>📦 물류센터 입고 및 접수 완료</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -6495,13 +6491,13 @@
         </is>
       </c>
       <c r="T49" t="n">
-        <v>351000</v>
+        <v>39840</v>
       </c>
       <c r="U49" t="n">
-        <v>235000</v>
+        <v>35000</v>
       </c>
       <c r="V49" t="n">
-        <v>116000</v>
+        <v>4840</v>
       </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
@@ -6538,12 +6534,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BW-2026-054</t>
+          <t>BW-2026-057</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BW260003</t>
+          <t>BW260006</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -6563,7 +6559,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Penny Korisko</t>
+          <t>Amanda Boyer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6661,12 +6657,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BW-2026-055</t>
+          <t>BW-2026-058</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BW260004</t>
+          <t>BW260007</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6686,7 +6682,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Armita Azari</t>
+          <t>Bella Glow Labs (Abigail Morales)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6716,19 +6712,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>25×20×10cm(1CTN)</t>
+          <t>33×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.009 CBM</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -6741,13 +6737,13 @@
         </is>
       </c>
       <c r="T51" t="n">
-        <v>39840</v>
+        <v>79680</v>
       </c>
       <c r="U51" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V51" t="n">
-        <v>4840</v>
+        <v>19680</v>
       </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
@@ -6779,17 +6775,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BW-2026-056</t>
+          <t>BW-2026-059</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BW260005</t>
+          <t>BW260008</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6804,17 +6800,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Breanna Ross</t>
+          <t>Jun Cheong</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>bf t</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6829,7 +6825,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -6839,19 +6835,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>21×19×9cm(1CTN)</t>
+          <t>45×31×16cm(1CTN)</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -6864,13 +6860,13 @@
         </is>
       </c>
       <c r="T52" t="n">
-        <v>39840</v>
+        <v>150000</v>
       </c>
       <c r="U52" t="n">
-        <v>35000</v>
+        <v>74000</v>
       </c>
       <c r="V52" t="n">
-        <v>4840</v>
+        <v>76000</v>
       </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
@@ -6883,16 +6879,26 @@
           <t>이상복</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>5332 Noel Drive Temple City, CA 91780</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>9099922845</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>3.45</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6902,17 +6908,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BW-2026-057</t>
+          <t>BW-2026-061</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BW260006</t>
+          <t>1ZRR43520326316852</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6927,12 +6933,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Amanda Boyer</t>
+          <t>Trisha Banusing</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6962,19 +6968,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>36×36×18cm(1CTN)</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.023 CBM</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -6983,17 +6989,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T53" t="n">
-        <v>79680</v>
+        <v>219200</v>
       </c>
       <c r="U53" t="n">
-        <v>60000</v>
+        <v>110000</v>
       </c>
       <c r="V53" t="n">
-        <v>19680</v>
+        <v>109200</v>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
@@ -7006,16 +7012,26 @@
           <t>이상복</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>134 S Seneca Circle Anaheim California 92805 USA</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>1 707-685-7724</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7025,17 +7041,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BW-2026-058</t>
+          <t>BW-2026-062</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BW260007</t>
+          <t>BW260011</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7050,12 +7066,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bella Glow Labs (Abigail Morales)</t>
+          <t>Alex Arrieta Lopez</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7080,24 +7096,24 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>33×21×13cm(1CTN)</t>
+          <t>49×35×22cm(1CTN) / 49×46×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>0.009 CBM</t>
+          <t>0.102 CBM</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -7106,19 +7122,23 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T54" t="n">
-        <v>79680</v>
+        <v>792640</v>
       </c>
       <c r="U54" t="n">
-        <v>60000</v>
+        <v>435000</v>
       </c>
       <c r="V54" t="n">
-        <v>19680</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
+        <v>357640</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7129,16 +7149,26 @@
           <t>이상복</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>8589 NW 54TH ST MIAMI, FL 33166-3322</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1 7862778309</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7153,12 +7183,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BW-2026-059</t>
+          <t>BW-2026-063</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BW260008</t>
+          <t>1ZRR43520311856663</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7173,17 +7203,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Jun Cheong</t>
+          <t>Rachelle Huemoeller</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>bf t</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7198,7 +7228,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -7208,19 +7238,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>45×31×16cm(1CTN)</t>
+          <t>54×25×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.038 CBM</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -7229,19 +7259,23 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T55" t="n">
-        <v>150000</v>
+        <v>326720</v>
       </c>
       <c r="U55" t="n">
-        <v>74000</v>
+        <v>210000</v>
       </c>
       <c r="V55" t="n">
-        <v>76000</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
+        <v>116720</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>화장품 의약품</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7255,22 +7289,22 @@
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>5332 Noel Drive Temple City, CA 91780</t>
+          <t>6279 Mahan drive, San Jose California 95123</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>9099922845</t>
+          <t>1 (408) 807-1185</t>
         </is>
       </c>
       <c r="AC55" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.45</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="56">
@@ -7286,12 +7320,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BW-2026-061</t>
+          <t>BW-2026-064</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1ZRR43520326316852</t>
+          <t>1ZRR43520316271642</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7311,12 +7345,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Trisha Banusing</t>
+          <t>Jacquline A</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7331,7 +7365,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -7341,19 +7375,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>36×36×18cm(1CTN)</t>
+          <t>49×35×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>0.023 CBM</t>
+          <t>0.079 CBM</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -7366,13 +7400,13 @@
         </is>
       </c>
       <c r="T56" t="n">
-        <v>219200</v>
+        <v>411120</v>
       </c>
       <c r="U56" t="n">
-        <v>110000</v>
+        <v>338400</v>
       </c>
       <c r="V56" t="n">
-        <v>109200</v>
+        <v>72720</v>
       </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr">
@@ -7388,22 +7422,22 @@
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>134 S Seneca Circle Anaheim California 92805 USA</t>
+          <t>555 Vwtrans Dr #201 Kyle,Tx 78640</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>1 707-685-7724</t>
+          <t>1 (512) 773-6361</t>
         </is>
       </c>
       <c r="AC56" t="n">
-        <v>3.5</v>
+        <v>17.3</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.5</v>
+        <v>17.3</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.5</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="57">
@@ -7419,12 +7453,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BW-2026-062</t>
+          <t>BW-2026-065</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BW260011</t>
+          <t>1ZRR43520316271642</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7444,12 +7478,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Alex Arrieta Lopez</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7464,7 +7498,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -7474,19 +7508,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>49×35×22cm(1CTN) / 49×46×28cm(1CTN)</t>
+          <t>21×35×45cm(1CTN) / 49×35×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.102 CBM</t>
+          <t>0.113 CBM</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="Q57" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -7499,17 +7533,17 @@
         </is>
       </c>
       <c r="T57" t="n">
-        <v>792640</v>
+        <v>1672320</v>
       </c>
       <c r="U57" t="n">
-        <v>435000</v>
+        <v>1305000</v>
       </c>
       <c r="V57" t="n">
-        <v>357640</v>
+        <v>367320</v>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>화장품 의약품</t>
+          <t>ups 1day 서비스요청건 kg당12000원 청구 완료</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -7525,22 +7559,22 @@
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>8589 NW 54TH ST MIAMI, FL 33166-3322</t>
+          <t>14411-B Export Rd,LAREDO TEXAS, USA,ZIP CODE 78045</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>1 7862778309</t>
+          <t>1 8182189089</t>
         </is>
       </c>
       <c r="AC57" t="n">
-        <v>15.2</v>
+        <v>47.8</v>
       </c>
       <c r="AD57" t="n">
-        <v>15.2</v>
+        <v>47.8</v>
       </c>
       <c r="AE57" t="n">
-        <v>15.2</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="58">
@@ -7556,12 +7590,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BW-2026-063</t>
+          <t>BW-2026-066</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1ZRR43520311856663</t>
+          <t>BW260015</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7576,12 +7610,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Rachelle Huemoeller</t>
+          <t>Kimberly Tapia</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -7611,19 +7645,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>54×25×28cm(1CTN)</t>
+          <t>35×28×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>0.038 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -7632,23 +7666,19 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T58" t="n">
-        <v>326720</v>
+        <v>199200</v>
       </c>
       <c r="U58" t="n">
-        <v>210000</v>
+        <v>135000</v>
       </c>
       <c r="V58" t="n">
-        <v>116720</v>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>화장품 의약품</t>
-        </is>
-      </c>
+        <v>64200</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7662,22 +7692,22 @@
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>6279 Mahan drive, San Jose California 95123</t>
+          <t>17320 Kingsbury St Granada Hills, CA 91344</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>1 (408) 807-1185</t>
+          <t>1-818-336-7713</t>
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>7.6</v>
+        <v>4.11</v>
       </c>
       <c r="AD58" t="n">
-        <v>7.6</v>
+        <v>4.11</v>
       </c>
       <c r="AE58" t="n">
-        <v>7.6</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="59">
@@ -7688,22 +7718,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>BW-2026-064</t>
+          <t>BW-2026-067</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1ZRR43520316271642</t>
+          <t>BW260016</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7713,22 +7743,22 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Jacquline A</t>
+          <t>余涛</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7738,7 +7768,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -7748,19 +7778,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>49×35×45cm(1CTN)</t>
+          <t>45×32×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>0.079 CBM</t>
+          <t>0.028 CBM</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -7773,13 +7803,13 @@
         </is>
       </c>
       <c r="T59" t="n">
-        <v>411120</v>
+        <v>150000</v>
       </c>
       <c r="U59" t="n">
-        <v>338400</v>
+        <v>103600</v>
       </c>
       <c r="V59" t="n">
-        <v>72720</v>
+        <v>46400</v>
       </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr">
@@ -7795,22 +7825,22 @@
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>555 Vwtrans Dr #201 Kyle,Tx 78640</t>
+          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>1 (512) 773-6361</t>
+          <t>17589745505</t>
         </is>
       </c>
       <c r="AC59" t="n">
-        <v>17.3</v>
+        <v>4.86</v>
       </c>
       <c r="AD59" t="n">
-        <v>17.3</v>
+        <v>4.86</v>
       </c>
       <c r="AE59" t="n">
-        <v>17.3</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="60">
@@ -7821,22 +7851,22 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BW-2026-065</t>
+          <t>BW-2026-068</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1ZRR43520316271642</t>
+          <t>BW260017</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7846,22 +7876,22 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>주식회사 조은로직스</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER</t>
+          <t>河美兰</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7871,29 +7901,29 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>21×35×45cm(1CTN) / 49×35×45cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0.113 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="Q60" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -7906,19 +7936,15 @@
         </is>
       </c>
       <c r="T60" t="n">
-        <v>1672320</v>
+        <v>480000</v>
       </c>
       <c r="U60" t="n">
-        <v>1305000</v>
+        <v>384000</v>
       </c>
       <c r="V60" t="n">
-        <v>367320</v>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>ups 1day 서비스요청건 kg당12000원 청구 완료</t>
-        </is>
-      </c>
+        <v>96000</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -7926,28 +7952,28 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>14411-B Export Rd,LAREDO TEXAS, USA,ZIP CODE 78045</t>
+          <t>东莞市寮步镇和合园汇富中心A座313室  收件人</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>1 8182189089</t>
+          <t>13480021737</t>
         </is>
       </c>
       <c r="AC60" t="n">
-        <v>47.8</v>
+        <v>32</v>
       </c>
       <c r="AD60" t="n">
-        <v>47.8</v>
+        <v>32</v>
       </c>
       <c r="AE60" t="n">
-        <v>47.8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -7958,22 +7984,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BW-2026-066</t>
+          <t>BW-2026-069</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BW260015</t>
+          <t>BW260018</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7983,12 +8009,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>맥익스프레스 인터내셔날(주)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Kimberly Tapia</t>
+          <t>金皓</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7998,7 +8024,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8008,29 +8034,29 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>35×28×22cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>295</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -8039,19 +8065,23 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T61" t="n">
-        <v>199200</v>
+        <v>5900000</v>
       </c>
       <c r="U61" t="n">
-        <v>135000</v>
+        <v>1475000</v>
       </c>
       <c r="V61" t="n">
-        <v>64200</v>
-      </c>
-      <c r="W61" t="inlineStr"/>
+        <v>4425000</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>인천시노 1톤차량 운임 50000원 비용지불</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr">
         <is>
           <t>이상복</t>
@@ -8065,22 +8095,22 @@
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>17320 Kingsbury St Granada Hills, CA 91344</t>
+          <t>山东省威海市环翠区怡园街道抚顺路 高发大厦 主楼 C区 401</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>1-818-336-7713</t>
+          <t>13906301025</t>
         </is>
       </c>
       <c r="AC61" t="n">
-        <v>4.11</v>
+        <v>295</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.11</v>
+        <v>295</v>
       </c>
       <c r="AE61" t="n">
-        <v>4.11</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62">
@@ -8091,22 +8121,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BW-2026-067</t>
+          <t>BW-2026-070</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BW260016</t>
+          <t>BW260019</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -8116,22 +8146,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>텐트러스트</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>余涛</t>
+          <t xml:space="preserve">Gina Sylvester </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8141,7 +8171,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -8151,19 +8181,19 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>45×32×19cm(1CTN)</t>
+          <t>22×19×10cm(1CTN)</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0.028 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -8176,13 +8206,13 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>150000</v>
+        <v>39840</v>
       </c>
       <c r="U62" t="n">
-        <v>103600</v>
+        <v>35000</v>
       </c>
       <c r="V62" t="n">
-        <v>46400</v>
+        <v>4840</v>
       </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr">
@@ -8192,28 +8222,28 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
+          <t>1093 Hawthorne Avenue, Beecher, IL 60401</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>17589745505</t>
+          <t>1-708-595-3553</t>
         </is>
       </c>
       <c r="AC62" t="n">
-        <v>4.86</v>
+        <v>0.72</v>
       </c>
       <c r="AD62" t="n">
-        <v>4.86</v>
+        <v>0.72</v>
       </c>
       <c r="AE62" t="n">
-        <v>4.86</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="63">
@@ -8224,22 +8254,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BW-2026-068</t>
+          <t>BW-2026-071</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BW260017</t>
+          <t>BW260020</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -8249,22 +8279,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>주식회사 조은로직스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>河美兰</t>
+          <t>Renay Scott</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8274,7 +8304,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -8284,19 +8314,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>34×20×20cm(1CTN)</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.014 CBM</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -8309,13 +8339,13 @@
         </is>
       </c>
       <c r="T63" t="n">
-        <v>480000</v>
+        <v>119520</v>
       </c>
       <c r="U63" t="n">
-        <v>384000</v>
+        <v>85000</v>
       </c>
       <c r="V63" t="n">
-        <v>96000</v>
+        <v>34520</v>
       </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr">
@@ -8325,28 +8355,28 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>东莞市寮步镇和合园汇富中心A座313室  收件人</t>
+          <t>619 Belleville Avenue Belleville, NJ 07109</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13480021737</t>
+          <t>1-862-336-5797</t>
         </is>
       </c>
       <c r="AC63" t="n">
-        <v>32</v>
+        <v>2.58</v>
       </c>
       <c r="AD63" t="n">
-        <v>32</v>
+        <v>2.58</v>
       </c>
       <c r="AE63" t="n">
-        <v>32</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="64">
@@ -8357,22 +8387,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BW-2026-069</t>
+          <t>BW-2026-072</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BW260018</t>
+          <t>BW260021</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -8382,12 +8412,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>맥익스프레스 인터내셔날(주)</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>金皓</t>
+          <t xml:space="preserve">Brenda A </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -8397,7 +8427,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8407,83 +8437,79 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
+          <t>24×20×10cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0.005 CBM</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>39840</v>
+      </c>
+      <c r="U64" t="n">
+        <v>35000</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4840</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>0.000 CBM</t>
-        </is>
-      </c>
-      <c r="P64" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>295</v>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T64" t="n">
-        <v>5900000</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1475000</v>
-      </c>
-      <c r="V64" t="n">
-        <v>4425000</v>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>인천시노 1톤차량 운임 50000원 비용지불</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>이상복</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>山东省威海市环翠区怡园街道抚顺路 高发大厦 主楼 C区 401</t>
+          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13906301025</t>
+          <t>1-512-489-7880</t>
         </is>
       </c>
       <c r="AC64" t="n">
-        <v>295</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AD64" t="n">
-        <v>295</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AE64" t="n">
-        <v>295</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -8499,12 +8525,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BW-2026-070</t>
+          <t>BW-2026-073</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BW260019</t>
+          <t>BW260022</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -8519,12 +8545,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gina Sylvester </t>
+          <t>Mylene Marquez</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8554,19 +8580,19 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>22×19×10cm(1CTN)</t>
+          <t>28×28×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.022 CBM</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -8579,13 +8605,13 @@
         </is>
       </c>
       <c r="T65" t="n">
-        <v>39840</v>
+        <v>199200</v>
       </c>
       <c r="U65" t="n">
-        <v>35000</v>
+        <v>110000</v>
       </c>
       <c r="V65" t="n">
-        <v>4840</v>
+        <v>89200</v>
       </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr">
@@ -8595,28 +8621,28 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1093 Hawthorne Avenue, Beecher, IL 60401</t>
+          <t>Your Spa LLC 18832 Christina Avenue Cerritos, CA 90703 United States</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>1-708-595-3553</t>
+          <t>+1 (562) 412-4328</t>
         </is>
       </c>
       <c r="AC65" t="n">
-        <v>0.72</v>
+        <v>3.5</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.72</v>
+        <v>3.5</v>
       </c>
       <c r="AE65" t="n">
-        <v>0.72</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="66">
@@ -8632,12 +8658,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BW-2026-071</t>
+          <t>BW-2026-074</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BW260020</t>
+          <t>BW260023</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -8652,12 +8678,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>아코글로벌</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Renay Scott</t>
+          <t>Jose Fernandez</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8687,19 +8713,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>34×20×20cm(1CTN)</t>
+          <t>26×18×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0.014 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -8712,13 +8738,13 @@
         </is>
       </c>
       <c r="T66" t="n">
-        <v>119520</v>
+        <v>79680</v>
       </c>
       <c r="U66" t="n">
-        <v>85000</v>
+        <v>60000</v>
       </c>
       <c r="V66" t="n">
-        <v>34520</v>
+        <v>19680</v>
       </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr">
@@ -8728,28 +8754,28 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>619 Belleville Avenue Belleville, NJ 07109</t>
+          <t>99 Van Buren St Newark NJ 07105 United States</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>1-862-336-5797</t>
+          <t>+1 (609) 331-6550</t>
         </is>
       </c>
       <c r="AC66" t="n">
-        <v>2.58</v>
+        <v>1.3</v>
       </c>
       <c r="AD66" t="n">
-        <v>2.58</v>
+        <v>1.3</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.58</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="67">
@@ -8765,12 +8791,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BW-2026-072</t>
+          <t>BW-2026-075</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BW260021</t>
+          <t>BW260024</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -8785,12 +8811,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>뷰메디스</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brenda A </t>
+          <t>Opus beauty</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8820,19 +8846,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>24×20×10cm(1CTN)</t>
+          <t>47×36×35cm(1CTN)</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.060 CBM</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -8845,13 +8871,13 @@
         </is>
       </c>
       <c r="T67" t="n">
-        <v>39840</v>
+        <v>468000</v>
       </c>
       <c r="U67" t="n">
-        <v>35000</v>
+        <v>285000</v>
       </c>
       <c r="V67" t="n">
-        <v>4840</v>
+        <v>183000</v>
       </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr">
@@ -8861,28 +8887,28 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
+          <t>4465 Wilshire Blvd. #103 Los Angeles CA 90010 USA</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>1-512-489-7880</t>
+          <t xml:space="preserve">+1 213 378 8996  </t>
         </is>
       </c>
       <c r="AC67" t="n">
-        <v>0.8100000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD67" t="n">
-        <v>0.8100000000000001</v>
+        <v>11</v>
       </c>
       <c r="AE67" t="n">
-        <v>0.8100000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -8898,12 +8924,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BW-2026-073</t>
+          <t>BW-2026-076</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BW260022</t>
+          <t>BW260025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8918,12 +8944,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Mylene Marquez</t>
+          <t>Lisa Czajko</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8953,19 +8979,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>28×28×28cm(1CTN)</t>
+          <t>47×37×34cm(1CTN)</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.022 CBM</t>
+          <t>0.059 CBM</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -8978,13 +9004,13 @@
         </is>
       </c>
       <c r="T68" t="n">
-        <v>199200</v>
+        <v>478080</v>
       </c>
       <c r="U68" t="n">
-        <v>110000</v>
+        <v>285000</v>
       </c>
       <c r="V68" t="n">
-        <v>89200</v>
+        <v>193080</v>
       </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr">
@@ -8994,28 +9020,28 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Your Spa LLC 18832 Christina Avenue Cerritos, CA 90703 United States</t>
+          <t>5 Toms way LaGrangeville NY 12540</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>+1 (562) 412-4328</t>
+          <t>1-347-739-2112</t>
         </is>
       </c>
       <c r="AC68" t="n">
-        <v>3.5</v>
+        <v>10.52</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.5</v>
+        <v>10.52</v>
       </c>
       <c r="AE68" t="n">
-        <v>3.5</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="69">
@@ -9031,12 +9057,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BW-2026-074</t>
+          <t>BW-2026-077</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BW260023</t>
+          <t>BW260026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -9051,12 +9077,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>아코글로벌</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Jose Fernandez</t>
+          <t>Jayde Lysne</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9086,12 +9112,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>26×18×15cm(1CTN)</t>
+          <t>21×33×14cm(1CTN)</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.010 CBM</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -9133,12 +9159,12 @@
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>99 Van Buren St Newark NJ 07105 United States</t>
+          <t>9 McDougall Dr Lincoln, ND 58504 USA</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>+1 (609) 331-6550</t>
+          <t>+17017718847</t>
         </is>
       </c>
       <c r="AC69" t="n">
@@ -9159,17 +9185,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BW-2026-075</t>
+          <t>BW-2026-078</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BW260024</t>
+          <t>BW260027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -9184,12 +9210,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>뷰메디스</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Opus beauty</t>
+          <t>Yahaira Monzon-Perez</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -9214,24 +9240,24 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>3 박스 (CTN)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>47×36×35cm(1CTN)</t>
+          <t>51×45×40cm(2CTN) / 36×35×25cm(1CTN)</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0.060 CBM</t>
+          <t>0.220 CBM</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="Q70" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -9244,13 +9270,13 @@
         </is>
       </c>
       <c r="T70" t="n">
-        <v>468000</v>
+        <v>1872480</v>
       </c>
       <c r="U70" t="n">
-        <v>285000</v>
+        <v>1185000</v>
       </c>
       <c r="V70" t="n">
-        <v>183000</v>
+        <v>687480</v>
       </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr">
@@ -9266,22 +9292,22 @@
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>4465 Wilshire Blvd. #103 Los Angeles CA 90010 USA</t>
+          <t>6036 Lowe Ln, Charlotte, NC, 28214</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t xml:space="preserve">+1 213 378 8996  </t>
+          <t>1-(980) 729 – 3258</t>
         </is>
       </c>
       <c r="AC70" t="n">
-        <v>11</v>
+        <v>46.19</v>
       </c>
       <c r="AD70" t="n">
-        <v>11</v>
+        <v>46.19</v>
       </c>
       <c r="AE70" t="n">
-        <v>11</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="71">
@@ -9292,17 +9318,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BW-2026-076</t>
+          <t>BW-2026-079</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BW260025</t>
+          <t>BW260028</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -9322,7 +9348,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Lisa Czajko</t>
+          <t xml:space="preserve">Elsa Paule   </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9352,19 +9378,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>47×37×34cm(1CTN)</t>
+          <t>51×45×40cm(1CTN)</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0.059 CBM</t>
+          <t>0.094 CBM</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q71" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -9377,13 +9403,13 @@
         </is>
       </c>
       <c r="T71" t="n">
-        <v>478080</v>
+        <v>756960</v>
       </c>
       <c r="U71" t="n">
-        <v>285000</v>
+        <v>410000</v>
       </c>
       <c r="V71" t="n">
-        <v>193080</v>
+        <v>346960</v>
       </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr">
@@ -9399,22 +9425,22 @@
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>5 Toms way LaGrangeville NY 12540</t>
+          <t>94 Leonard st,2, Jersey City, new jersey, 07307</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>1-347-739-2112</t>
+          <t>1-301-401-3096</t>
         </is>
       </c>
       <c r="AC71" t="n">
-        <v>10.52</v>
+        <v>15.57</v>
       </c>
       <c r="AD71" t="n">
-        <v>10.52</v>
+        <v>15.57</v>
       </c>
       <c r="AE71" t="n">
-        <v>10.52</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="72">
@@ -9425,17 +9451,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BW-2026-077</t>
+          <t>BW-2026-080</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BW260026</t>
+          <t>BW260029</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -9455,7 +9481,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Jayde Lysne</t>
+          <t>Samara Novaes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9485,12 +9511,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>21×33×14cm(1CTN)</t>
+          <t>33.5×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.010 CBM</t>
+          <t>0.094 CBM</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -9526,28 +9552,28 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>9 McDougall Dr Lincoln, ND 58504 USA</t>
+          <t>11230 Ranch Creek Ter, Apt 311 Bradenton, FL, 34211</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>+17017718847</t>
+          <t>1-689-266-7610</t>
         </is>
       </c>
       <c r="AC72" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
       <c r="AD72" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="73">
@@ -9563,12 +9589,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BW-2026-078</t>
+          <t>BW-2026-081</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BW260027</t>
+          <t>BW260030</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -9588,7 +9614,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Yahaira Monzon-Perez</t>
+          <t>Sarah Larson</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -9613,24 +9639,24 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>3 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>51×45×40cm(2CTN) / 36×35×25cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0.220 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -9643,13 +9669,13 @@
         </is>
       </c>
       <c r="T73" t="n">
-        <v>1872480</v>
+        <v>39840</v>
       </c>
       <c r="U73" t="n">
-        <v>1185000</v>
+        <v>35000</v>
       </c>
       <c r="V73" t="n">
-        <v>687480</v>
+        <v>4840</v>
       </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr">
@@ -9659,28 +9685,28 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>6036 Lowe Ln, Charlotte, NC, 28214</t>
+          <t>18544 E Apricot Lane Queen Creek, AZ 85142</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>1-(980) 729 – 3258</t>
+          <t>1-602-369-0694</t>
         </is>
       </c>
       <c r="AC73" t="n">
-        <v>46.19</v>
+        <v>0.44</v>
       </c>
       <c r="AD73" t="n">
-        <v>46.19</v>
+        <v>0.44</v>
       </c>
       <c r="AE73" t="n">
-        <v>46.19</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="74">
@@ -9696,12 +9722,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BW-2026-079</t>
+          <t>BW-2026-082</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BW260028</t>
+          <t>BW260031</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -9721,7 +9747,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elsa Paule   </t>
+          <t>Dr. Kyle Uhlich</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9751,19 +9777,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>51×45×40cm(1CTN)</t>
+          <t>22×19×9cm(1CTN)</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0.094 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="Q74" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -9776,13 +9802,13 @@
         </is>
       </c>
       <c r="T74" t="n">
-        <v>756960</v>
+        <v>278880</v>
       </c>
       <c r="U74" t="n">
-        <v>410000</v>
+        <v>185000</v>
       </c>
       <c r="V74" t="n">
-        <v>346960</v>
+        <v>93880</v>
       </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr">
@@ -9792,28 +9818,28 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>94 Leonard st,2, Jersey City, new jersey, 07307</t>
+          <t>403 SHADOW LANE SAPULPA, OK 74066</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>1-301-401-3096</t>
+          <t>1-405-985-1644</t>
         </is>
       </c>
       <c r="AC74" t="n">
-        <v>15.57</v>
+        <v>6.4</v>
       </c>
       <c r="AD74" t="n">
-        <v>15.57</v>
+        <v>6.4</v>
       </c>
       <c r="AE74" t="n">
-        <v>15.57</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="75">
@@ -9829,12 +9855,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BW-2026-080</t>
+          <t>BW-2026-083</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BW260029</t>
+          <t>BW260032</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9854,7 +9880,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Samara Novaes</t>
+          <t>Madison Berberich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9884,16 +9910,16 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>33.5×21×13cm(1CTN)</t>
+          <t>33×21×14cm(1CTN)</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>0.094 CBM</t>
+          <t>0.010 CBM</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -9909,13 +9935,13 @@
         </is>
       </c>
       <c r="T75" t="n">
-        <v>79680</v>
+        <v>119520</v>
       </c>
       <c r="U75" t="n">
         <v>60000</v>
       </c>
       <c r="V75" t="n">
-        <v>19680</v>
+        <v>59520</v>
       </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
@@ -9925,28 +9951,28 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>11230 Ranch Creek Ter, Apt 311 Bradenton, FL, 34211</t>
+          <t>734 McCormick Ln Cincinnati, OH 45245 United States</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>1-689-266-7610</t>
+          <t>5136094841</t>
         </is>
       </c>
       <c r="AC75" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="AD75" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="AE75" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="76">
@@ -9962,12 +9988,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BW-2026-081</t>
+          <t>BW-2026-084</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BW260030</t>
+          <t>BW260033</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -9982,12 +10008,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sarah Larson</t>
+          <t>Bronislava Popovetsky</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -10012,24 +10038,24 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>49×35×38cm(2CTN)</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.134 CBM</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -10042,13 +10068,13 @@
         </is>
       </c>
       <c r="T76" t="n">
-        <v>39840</v>
+        <v>1007680</v>
       </c>
       <c r="U76" t="n">
-        <v>35000</v>
+        <v>585000</v>
       </c>
       <c r="V76" t="n">
-        <v>4840</v>
+        <v>422680</v>
       </c>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr">
@@ -10058,28 +10084,28 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>18544 E Apricot Lane Queen Creek, AZ 85142</t>
+          <t>2549 Linden Street Bellmore, NY 11710</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>1-602-369-0694</t>
+          <t>1 (646) 407-9686</t>
         </is>
       </c>
       <c r="AC76" t="n">
-        <v>0.44</v>
+        <v>15.4</v>
       </c>
       <c r="AD76" t="n">
-        <v>0.44</v>
+        <v>15.4</v>
       </c>
       <c r="AE76" t="n">
-        <v>0.44</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="77">
@@ -10095,12 +10121,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BW-2026-082</t>
+          <t>BW-2026-085</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BW260031</t>
+          <t>BW260034</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -10115,12 +10141,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Dr. Kyle Uhlich</t>
+          <t>Maria Leonora A Dila</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -10150,19 +10176,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>22×19×9cm(1CTN)</t>
+          <t>36×36×19cm(1CTN)</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.025 CBM</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q77" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -10175,13 +10201,13 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>278880</v>
+        <v>255040</v>
       </c>
       <c r="U77" t="n">
-        <v>185000</v>
+        <v>135000</v>
       </c>
       <c r="V77" t="n">
-        <v>93880</v>
+        <v>120040</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">
@@ -10191,28 +10217,28 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>403 SHADOW LANE SAPULPA, OK 74066</t>
+          <t>31500 Grape St STE 3 Lake Elsinore, CA 92532</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>1-405-985-1644</t>
+          <t>1 714-512-1776</t>
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="AD77" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
       <c r="AE77" t="n">
-        <v>6.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="78">
@@ -10228,12 +10254,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BW-2026-083</t>
+          <t>BW-2026-086</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BW260032</t>
+          <t>BW260035</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -10248,12 +10274,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Madison Berberich</t>
+          <t>Sharon Seng</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -10283,19 +10309,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>33×21×14cm(1CTN)</t>
+          <t>49×36×23cm(1CTN)</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0.010 CBM</t>
+          <t>0.042 CBM</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -10308,13 +10334,13 @@
         </is>
       </c>
       <c r="T78" t="n">
-        <v>119520</v>
+        <v>362560</v>
       </c>
       <c r="U78" t="n">
-        <v>60000</v>
+        <v>210000</v>
       </c>
       <c r="V78" t="n">
-        <v>59520</v>
+        <v>152560</v>
       </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
@@ -10330,22 +10356,22 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>734 McCormick Ln Cincinnati, OH 45245 United States</t>
+          <t>921 Palo Cedro Dr Corona, California  92879</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>5136094841</t>
+          <t>1 (657) 527-2068</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="AD78" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
@@ -10361,12 +10387,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BW-2026-084</t>
+          <t>BW-2026-087</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BW260033</t>
+          <t>BW260036</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -10386,12 +10412,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Bronislava Popovetsky</t>
+          <t>DAMIAN RENATO JESUS MALO JUVER 8182189089</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10406,29 +10432,29 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>19박스 (CTN)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>49×35×38cm(2CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0.134 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>27</v>
+        <v>251</v>
       </c>
       <c r="Q79" t="n">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -10441,13 +10467,13 @@
         </is>
       </c>
       <c r="T79" t="n">
-        <v>1007680</v>
+        <v>5732840</v>
       </c>
       <c r="U79" t="n">
-        <v>585000</v>
+        <v>4681200</v>
       </c>
       <c r="V79" t="n">
-        <v>422680</v>
+        <v>1051640</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
@@ -10463,22 +10489,18 @@
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2549 Linden Street Bellmore, NY 11710</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>1 (646) 407-9686</t>
-        </is>
-      </c>
+          <t>DAMIAN RENATO JESUS MALO JUVER # B 14411 EXPORT RD LAREDO TX 78045-7945</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="n">
-        <v>15.4</v>
+        <v>251</v>
       </c>
       <c r="AD79" t="n">
-        <v>15.4</v>
+        <v>251</v>
       </c>
       <c r="AE79" t="n">
-        <v>15.4</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80">
@@ -10489,17 +10511,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BW-2026-085</t>
+          <t>BW-2026-088</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BW260034</t>
+          <t>BW260037</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -10514,12 +10536,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Maria Leonora A Dila</t>
+          <t>Glenda King</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -10549,19 +10571,19 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>36×36×19cm(1CTN)</t>
+          <t>27×19×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0.025 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -10574,13 +10596,13 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>255040</v>
+        <v>79680</v>
       </c>
       <c r="U80" t="n">
-        <v>135000</v>
+        <v>60000</v>
       </c>
       <c r="V80" t="n">
-        <v>120040</v>
+        <v>19680</v>
       </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr">
@@ -10596,22 +10618,22 @@
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>31500 Grape St STE 3 Lake Elsinore, CA 92532</t>
+          <t>99 Glendale Park Rochester NY 14613</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>1 714-512-1776</t>
+          <t>1-585-730-9288</t>
         </is>
       </c>
       <c r="AC80" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD80" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="81">
@@ -10622,22 +10644,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BW-2026-086</t>
+          <t>BW-2026-089</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BW260035</t>
+          <t>BW260038</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -10647,22 +10669,22 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sharon Seng</t>
+          <t>张永学</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>항공(Air)</t>
+          <t>해상(LCL)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10672,7 +10694,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -10682,19 +10704,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>49×36×23cm(1CTN)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0.042 CBM</t>
+          <t>0.000 CBM</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q81" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -10703,17 +10725,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>미수</t>
+          <t>수금완료</t>
         </is>
       </c>
       <c r="T81" t="n">
-        <v>362560</v>
+        <v>102000</v>
       </c>
       <c r="U81" t="n">
-        <v>210000</v>
+        <v>84000</v>
       </c>
       <c r="V81" t="n">
-        <v>152560</v>
+        <v>18000</v>
       </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
@@ -10723,28 +10745,28 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>921 Palo Cedro Dr Corona, California  92879</t>
+          <t xml:space="preserve">辽宁省大连市开发区马桥子街道赤峰街亿锋广场三期10号楼 </t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>1 (657) 527-2068</t>
+          <t>18640817665</t>
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AD81" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE81" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
@@ -10755,17 +10777,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BW-2026-087</t>
+          <t>BW-2026-090</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BW260036</t>
+          <t>BW260039</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -10780,17 +10802,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER 8182189089</t>
+          <t xml:space="preserve">Mayra Armenta   </t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10805,29 +10827,29 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>19박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>21.5×19×9.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.004 CBM</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>251</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>249</v>
+        <v>1</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -10840,13 +10862,13 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>5732840</v>
+        <v>39840</v>
       </c>
       <c r="U82" t="n">
-        <v>4681200</v>
+        <v>35000</v>
       </c>
       <c r="V82" t="n">
-        <v>1051640</v>
+        <v>4840</v>
       </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr">
@@ -10856,24 +10878,28 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>DAMIAN RENATO JESUS MALO JUVER # B 14411 EXPORT RD LAREDO TX 78045-7945</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr"/>
+          <t>1407 Magnolia Ave San Bernardino ca 92411</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>1-909-314-3403</t>
+        </is>
+      </c>
       <c r="AC82" t="n">
-        <v>251</v>
+        <v>0.83</v>
       </c>
       <c r="AD82" t="n">
-        <v>251</v>
+        <v>0.83</v>
       </c>
       <c r="AE82" t="n">
-        <v>249</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="83">
@@ -10884,17 +10910,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BW-2026-088</t>
+          <t>BW-2026-091</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BW260037</t>
+          <t>BW260040</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -10914,7 +10940,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Glenda King</t>
+          <t xml:space="preserve">Daphne Ortiz  </t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -10944,19 +10970,19 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>27×19×15cm(1CTN)</t>
+          <t>34.5×21×20cm(1CTN)</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.014 CBM</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -10969,13 +10995,13 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>79680</v>
+        <v>119520</v>
       </c>
       <c r="U83" t="n">
-        <v>60000</v>
+        <v>85000</v>
       </c>
       <c r="V83" t="n">
-        <v>19680</v>
+        <v>34520</v>
       </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr">
@@ -10985,28 +11011,28 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>99 Glendale Park Rochester NY 14613</t>
+          <t>154 State Street Penns Grove, NJ 08069, USA</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>1-585-730-9288</t>
+          <t>1-856-275-1158</t>
         </is>
       </c>
       <c r="AC83" t="n">
-        <v>1.39</v>
+        <v>2.68</v>
       </c>
       <c r="AD83" t="n">
-        <v>1.39</v>
+        <v>2.68</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.39</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="84">
@@ -11017,22 +11043,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BW-2026-089</t>
+          <t>BW-2026-092</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BW260038</t>
+          <t>BW260041</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -11042,22 +11068,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>글로우필메디앤코</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>张永学</t>
+          <t xml:space="preserve">Alissa Fender </t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>윤세형</t>
+          <t>(주)카스익스프레스</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>해상(LCL)</t>
+          <t>항공(Air)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -11067,7 +11093,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>보톡스</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -11077,19 +11103,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20.5×13×8cm(1CTN)</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0.000 CBM</t>
+          <t>0.002 CBM</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -11098,17 +11124,17 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>수금완료</t>
+          <t>미수</t>
         </is>
       </c>
       <c r="T84" t="n">
-        <v>102000</v>
+        <v>39840</v>
       </c>
       <c r="U84" t="n">
-        <v>84000</v>
+        <v>35000</v>
       </c>
       <c r="V84" t="n">
-        <v>18000</v>
+        <v>4840</v>
       </c>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr">
@@ -11124,22 +11150,22 @@
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr">
         <is>
-          <t xml:space="preserve">辽宁省大连市开发区马桥子街道赤峰街亿锋广场三期10号楼 </t>
+          <t>283 Brookstone Way, Jacksonville, NC, 28546, USA</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18640817665</t>
+          <t>1-910-381-9517</t>
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>12</v>
+        <v>0.49</v>
       </c>
       <c r="AD84" t="n">
-        <v>12</v>
+        <v>0.49</v>
       </c>
       <c r="AE84" t="n">
-        <v>12</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="85">
@@ -11155,12 +11181,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BW-2026-090</t>
+          <t>BW-2026-093</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BW260039</t>
+          <t>BW260042</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -11180,7 +11206,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mayra Armenta   </t>
+          <t>Quadrat Asuni</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -11210,19 +11236,19 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>21.5×19×9.5cm(1CTN)</t>
+          <t>26×18.5×15cm(1CTN)</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>0.004 CBM</t>
+          <t>0.005 CBM</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -11235,13 +11261,13 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>39840</v>
+        <v>79680</v>
       </c>
       <c r="U85" t="n">
-        <v>35000</v>
+        <v>60000</v>
       </c>
       <c r="V85" t="n">
-        <v>4840</v>
+        <v>19680</v>
       </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
@@ -11251,28 +11277,28 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>1407 Magnolia Ave San Bernardino ca 92411</t>
+          <t>1955 Waters Branch Drive, Missouri City tx 77459</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>1-909-314-3403</t>
+          <t>1-346-871-8692</t>
         </is>
       </c>
       <c r="AC85" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="AD85" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
       <c r="AE85" t="n">
-        <v>0.83</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="86">
@@ -11288,12 +11314,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BW-2026-091</t>
+          <t>BW-2026-094</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BW260040</t>
+          <t>BW260043</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -11313,7 +11339,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Daphne Ortiz  </t>
+          <t>Yordan Fernandez</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -11343,19 +11369,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>34.5×21×20cm(1CTN)</t>
+          <t>33.5×26×20cm(1CTN)</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>0.014 CBM</t>
+          <t>0.017 CBM</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -11368,13 +11394,13 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>119520</v>
+        <v>199200</v>
       </c>
       <c r="U86" t="n">
-        <v>85000</v>
+        <v>135000</v>
       </c>
       <c r="V86" t="n">
-        <v>34520</v>
+        <v>64200</v>
       </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr">
@@ -11390,22 +11416,22 @@
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>154 State Street Penns Grove, NJ 08069, USA</t>
+          <t>3952 Cocoplum CIR #3643 E Karanda III Coconut Creek Florida USA, Zip 33063</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>1-856-275-1158</t>
+          <t>1-786-961-5525</t>
         </is>
       </c>
       <c r="AC86" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="AD86" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="AE86" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -11421,12 +11447,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BW-2026-092</t>
+          <t>BW-2026-095</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BW260041</t>
+          <t>BW260044</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -11441,12 +11467,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alissa Fender </t>
+          <t>Jose Diaz</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -11471,24 +11497,24 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>2 박스 (CTN)</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>20.5×13×8cm(1CTN)</t>
+          <t>41×29.5×39.5cm(2CTN)</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>0.002 CBM</t>
+          <t>0.096 CBM</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Q87" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -11501,13 +11527,13 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>39840</v>
+        <v>756800</v>
       </c>
       <c r="U87" t="n">
-        <v>35000</v>
+        <v>410000</v>
       </c>
       <c r="V87" t="n">
-        <v>4840</v>
+        <v>346800</v>
       </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr">
@@ -11517,28 +11543,28 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>283 Brookstone Way, Jacksonville, NC, 28546, USA</t>
+          <t>5530 NW 72nd Ave. IMS260133. Miami, Florida 33195.</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>1-910-381-9517</t>
+          <t>1 (407) 686-6492</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>0.49</v>
+        <v>11.54</v>
       </c>
       <c r="AD87" t="n">
-        <v>0.49</v>
+        <v>11.54</v>
       </c>
       <c r="AE87" t="n">
-        <v>0.49</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="88">
@@ -11554,12 +11580,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BW-2026-093</t>
+          <t>BW-2026-096</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BW260042</t>
+          <t>BW260045</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -11574,12 +11600,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Quadrat Asuni</t>
+          <t>Carol May Pareja</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -11609,19 +11635,19 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>26×18.5×15cm(1CTN)</t>
+          <t>50×36.5×35cm(1CTN)</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>0.005 CBM</t>
+          <t>0.064 CBM</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q88" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -11634,13 +11660,13 @@
         </is>
       </c>
       <c r="T88" t="n">
-        <v>79680</v>
+        <v>505920</v>
       </c>
       <c r="U88" t="n">
-        <v>60000</v>
+        <v>310000</v>
       </c>
       <c r="V88" t="n">
-        <v>19680</v>
+        <v>195920</v>
       </c>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr">
@@ -11650,28 +11676,28 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>1955 Waters Branch Drive, Missouri City tx 77459</t>
+          <t>8979 Barton St, Riverside, CA USA 92508</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>1-346-871-8692</t>
+          <t>1 (919) 710-3357</t>
         </is>
       </c>
       <c r="AC88" t="n">
-        <v>1.51</v>
+        <v>11.92</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.51</v>
+        <v>11.92</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.51</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="89">
@@ -11687,12 +11713,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>BW-2026-094</t>
+          <t>BW-2026-097</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BW260043</t>
+          <t>BW260046</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11707,12 +11733,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>글로우필메디앤코</t>
+          <t>넥서스파마 주식회사</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Yordan Fernandez</t>
+          <t>Ching Hanapin</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -11742,19 +11768,19 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>33.5×26×20cm(1CTN)</t>
+          <t>51×37×32cm(1CTN)</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>0.017 CBM</t>
+          <t>0.060 CBM</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q89" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -11767,13 +11793,13 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>199200</v>
+        <v>505920</v>
       </c>
       <c r="U89" t="n">
-        <v>135000</v>
+        <v>310000</v>
       </c>
       <c r="V89" t="n">
-        <v>64200</v>
+        <v>195920</v>
       </c>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr">
@@ -11783,28 +11809,28 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr"/>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>3952 Cocoplum CIR #3643 E Karanda III Coconut Creek Florida USA, Zip 33063</t>
+          <t>2048 Oliva Ct, Colton, CA 92324</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>1-786-961-5525</t>
+          <t>1 (909) 709-3550</t>
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>5</v>
+        <v>11.84</v>
       </c>
       <c r="AD89" t="n">
-        <v>5</v>
+        <v>11.84</v>
       </c>
       <c r="AE89" t="n">
-        <v>5</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="90">
@@ -11820,12 +11846,12 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BW-2026-095</t>
+          <t>BW-2026-098</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BW260044</t>
+          <t>BW260047</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -11845,7 +11871,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Jose Diaz</t>
+          <t>Jayson Ayan</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11870,24 +11896,24 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2 박스 (CTN)</t>
+          <t>1 박스 (CTN)</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>41×29.5×39.5cm(2CTN)</t>
+          <t>50×37×22.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0.096 CBM</t>
+          <t>0.042 CBM</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Q90" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
@@ -11900,13 +11926,13 @@
         </is>
       </c>
       <c r="T90" t="n">
-        <v>756800</v>
+        <v>470080</v>
       </c>
       <c r="U90" t="n">
-        <v>410000</v>
+        <v>310000</v>
       </c>
       <c r="V90" t="n">
-        <v>346800</v>
+        <v>160080</v>
       </c>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr">
@@ -11922,22 +11948,22 @@
       <c r="Z90" t="inlineStr"/>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>5530 NW 72nd Ave. IMS260133. Miami, Florida 33195.</t>
+          <t>8716 55th Ave, Elmhurst, NY 11373</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>1 (407) 686-6492</t>
+          <t>1 347 446 4492</t>
         </is>
       </c>
       <c r="AC90" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
       <c r="AD90" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
       <c r="AE90" t="n">
-        <v>11.54</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="91">
@@ -11953,12 +11979,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BW-2026-096</t>
+          <t>BW-2026-099</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BW260045</t>
+          <t>BW260048</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -11978,7 +12004,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Carol May Pareja</t>
+          <t>Sharmaine Willis</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -12008,19 +12034,19 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>50×36.5×35cm(1CTN)</t>
+          <t>49.5×36.5×22cm(1CTN)</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>0.064 CBM</t>
+          <t>0.040 CBM</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q91" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -12033,13 +12059,13 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>505920</v>
+        <v>326720</v>
       </c>
       <c r="U91" t="n">
-        <v>310000</v>
+        <v>185000</v>
       </c>
       <c r="V91" t="n">
-        <v>195920</v>
+        <v>141720</v>
       </c>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr">
@@ -12049,28 +12075,28 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr"/>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>8979 Barton St, Riverside, CA USA 92508</t>
+          <t>3250 Wuthering Cir, Grand Prairie, TX 75052</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>1 (919) 710-3357</t>
+          <t>1 5054230759</t>
         </is>
       </c>
       <c r="AC91" t="n">
-        <v>11.92</v>
+        <v>5.64</v>
       </c>
       <c r="AD91" t="n">
-        <v>11.92</v>
+        <v>5.64</v>
       </c>
       <c r="AE91" t="n">
-        <v>11.92</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="92">
@@ -12086,12 +12112,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BW-2026-097</t>
+          <t>BW-2026-100</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BW260046</t>
+          <t>BW260049</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -12111,7 +12137,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Ching Hanapin</t>
+          <t>Evita Lois Abendan</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -12141,19 +12167,19 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>51×37×32cm(1CTN)</t>
+          <t>27×19×16cm(1CTN)</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>0.060 CBM</t>
+          <t>0.008 CBM</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -12166,13 +12192,13 @@
         </is>
       </c>
       <c r="T92" t="n">
-        <v>505920</v>
+        <v>111680</v>
       </c>
       <c r="U92" t="n">
-        <v>310000</v>
+        <v>60000</v>
       </c>
       <c r="V92" t="n">
-        <v>195920</v>
+        <v>51680</v>
       </c>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr">
@@ -12188,22 +12214,22 @@
       <c r="Z92" t="inlineStr"/>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2048 Oliva Ct, Colton, CA 92324</t>
+          <t xml:space="preserve"> 16825 Sunny Ridge ct. cerritos ca 90703</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>1 (909) 709-3550</t>
+          <t>15622506278</t>
         </is>
       </c>
       <c r="AC92" t="n">
-        <v>11.84</v>
+        <v>1.18</v>
       </c>
       <c r="AD92" t="n">
-        <v>11.84</v>
+        <v>1.18</v>
       </c>
       <c r="AE92" t="n">
-        <v>11.84</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="93">
@@ -12219,12 +12245,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BW-2026-098</t>
+          <t>BW-2026-101</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>BW260047</t>
+          <t>BW260050</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -12244,7 +12270,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Jayson Ayan</t>
+          <t>Jenny Torress</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -12274,19 +12300,19 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>50×37×22.5cm(1CTN)</t>
+          <t>49.5×36.5×22.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>0.042 CBM</t>
+          <t>0.041 CBM</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Q93" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -12299,13 +12325,13 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>470080</v>
+        <v>362560</v>
       </c>
       <c r="U93" t="n">
-        <v>310000</v>
+        <v>185000</v>
       </c>
       <c r="V93" t="n">
-        <v>160080</v>
+        <v>177560</v>
       </c>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr">
@@ -12321,22 +12347,22 @@
       <c r="Z93" t="inlineStr"/>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>8716 55th Ave, Elmhurst, NY 11373</t>
+          <t>1500 Briggs St Apt 8 Daly City  CA 94015</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>1 347 446 4492</t>
+          <t>1 (415) 954-2774</t>
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>11.62</v>
+        <v>4.86</v>
       </c>
       <c r="AD93" t="n">
-        <v>11.62</v>
+        <v>4.86</v>
       </c>
       <c r="AE93" t="n">
-        <v>11.62</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="94">
@@ -12352,12 +12378,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BW-2026-099</t>
+          <t>BW-2026-102</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BW260048</t>
+          <t>BW260051</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -12377,7 +12403,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sharmaine Willis</t>
+          <t>Laura Swann</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -12407,19 +12433,19 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>49.5×36.5×22cm(1CTN)</t>
+          <t>50×36.5×45.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>0.040 CBM</t>
+          <t>0.083 CBM</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Q94" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -12432,13 +12458,13 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>326720</v>
+        <v>649280</v>
       </c>
       <c r="U94" t="n">
-        <v>185000</v>
+        <v>360000</v>
       </c>
       <c r="V94" t="n">
-        <v>141720</v>
+        <v>289280</v>
       </c>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr">
@@ -12448,28 +12474,28 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr"/>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>3250 Wuthering Cir, Grand Prairie, TX 75052</t>
+          <t>"4170 Blackheath Dr Bartlett, TN 38135"</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>1 5054230759</t>
+          <t>(901) 503‑8919</t>
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>5.64</v>
+        <v>10.6</v>
       </c>
       <c r="AD94" t="n">
-        <v>5.64</v>
+        <v>10.6</v>
       </c>
       <c r="AE94" t="n">
-        <v>5.64</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="95">
@@ -12485,12 +12511,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BW-2026-100</t>
+          <t>BW-2026-103</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>BW260049</t>
+          <t>BW260052</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -12510,7 +12536,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Evita Lois Abendan</t>
+          <t>Michael Soriano</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -12540,19 +12566,19 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>27×19×16cm(1CTN)</t>
+          <t>49×37×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>0.008 CBM</t>
+          <t>0.082 CBM</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -12565,13 +12591,13 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>111680</v>
+        <v>649280</v>
       </c>
       <c r="U95" t="n">
-        <v>60000</v>
+        <v>435000</v>
       </c>
       <c r="V95" t="n">
-        <v>51680</v>
+        <v>214280</v>
       </c>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr">
@@ -12587,22 +12613,22 @@
       <c r="Z95" t="inlineStr"/>
       <c r="AA95" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 16825 Sunny Ridge ct. cerritos ca 90703</t>
+          <t>35215 Orchard Trl Fallbrook, CA 92028</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15622506278</t>
+          <t>1 (858) 471-6674</t>
         </is>
       </c>
       <c r="AC95" t="n">
-        <v>1.18</v>
+        <v>16.18</v>
       </c>
       <c r="AD95" t="n">
-        <v>1.18</v>
+        <v>16.18</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.18</v>
+        <v>16.18</v>
       </c>
     </row>
     <row r="96">
@@ -12618,12 +12644,12 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BW-2026-101</t>
+          <t>BW-2026-104</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BW260050</t>
+          <t>BW260053</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -12643,7 +12669,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Jenny Torress</t>
+          <t>Brea A.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -12673,19 +12699,19 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>49.5×36.5×22.5cm(1CTN)</t>
+          <t>44×38×26.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>0.041 CBM</t>
+          <t>0.044 CBM</t>
         </is>
       </c>
       <c r="P96" t="n">
         <v>9</v>
       </c>
       <c r="Q96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -12701,10 +12727,10 @@
         <v>362560</v>
       </c>
       <c r="U96" t="n">
-        <v>185000</v>
+        <v>235000</v>
       </c>
       <c r="V96" t="n">
-        <v>177560</v>
+        <v>127560</v>
       </c>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr">
@@ -12720,22 +12746,22 @@
       <c r="Z96" t="inlineStr"/>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>1500 Briggs St Apt 8 Daly City  CA 94015</t>
+          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>1 (415) 954-2774</t>
+          <t>1 (512) 773-6361</t>
         </is>
       </c>
       <c r="AC96" t="n">
-        <v>4.86</v>
+        <v>8.82</v>
       </c>
       <c r="AD96" t="n">
-        <v>4.86</v>
+        <v>8.82</v>
       </c>
       <c r="AE96" t="n">
-        <v>4.86</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="97">
@@ -12751,12 +12777,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BW-2026-102</t>
+          <t>BW-2026-105</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>BW260051</t>
+          <t>BW260054</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -12776,7 +12802,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Laura Swann</t>
+          <t>Adela Maturan</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12806,19 +12832,19 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>50×36.5×45.5cm(1CTN)</t>
+          <t>40×33×39cm(1CTN)</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0.083 CBM</t>
+          <t>0.051 CBM</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q97" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -12831,13 +12857,13 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>649280</v>
+        <v>434240</v>
       </c>
       <c r="U97" t="n">
-        <v>360000</v>
+        <v>260000</v>
       </c>
       <c r="V97" t="n">
-        <v>289280</v>
+        <v>174240</v>
       </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr">
@@ -12853,22 +12879,22 @@
       <c r="Z97" t="inlineStr"/>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>"4170 Blackheath Dr Bartlett, TN 38135"</t>
+          <t>3133 Carlos Dr. Dunedin Fl 34698</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>(901) 503‑8919</t>
+          <t>1 (718) 564-5433</t>
         </is>
       </c>
       <c r="AC97" t="n">
-        <v>10.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AD97" t="n">
-        <v>10.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE97" t="n">
-        <v>10.6</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="98">
@@ -12884,12 +12910,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BW-2026-103</t>
+          <t>BW-2026-106</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BW260052</t>
+          <t>BW260055</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -12909,7 +12935,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Michael Soriano</t>
+          <t>Norriemil Pineda</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12939,19 +12965,19 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>49×37×45cm(1CTN)</t>
+          <t>36×36×18cm(1CTN)</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>0.082 CBM</t>
+          <t>0.023 CBM</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="Q98" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
@@ -12964,13 +12990,13 @@
         </is>
       </c>
       <c r="T98" t="n">
-        <v>649280</v>
+        <v>219200</v>
       </c>
       <c r="U98" t="n">
-        <v>435000</v>
+        <v>135000</v>
       </c>
       <c r="V98" t="n">
-        <v>214280</v>
+        <v>84200</v>
       </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr">
@@ -12986,22 +13012,22 @@
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>35215 Orchard Trl Fallbrook, CA 92028</t>
+          <t>31215 Windstone Dr. Winchester CA 92596 USA</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>1 (858) 471-6674</t>
+          <t>1 (951) 795-8172</t>
         </is>
       </c>
       <c r="AC98" t="n">
-        <v>16.18</v>
+        <v>4.63</v>
       </c>
       <c r="AD98" t="n">
-        <v>16.18</v>
+        <v>4.63</v>
       </c>
       <c r="AE98" t="n">
-        <v>16.18</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="99">
@@ -13017,12 +13043,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BW-2026-104</t>
+          <t>BW-2026-107</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>BW260053</t>
+          <t>BW260056</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -13042,7 +13068,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Brea A.</t>
+          <t>Devine Galingan</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -13072,19 +13098,19 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>44×38×26.5cm(1CTN)</t>
+          <t>26×36×28.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0.044 CBM</t>
+          <t>0.027 CBM</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
@@ -13097,13 +13123,13 @@
         </is>
       </c>
       <c r="T99" t="n">
-        <v>362560</v>
+        <v>255040</v>
       </c>
       <c r="U99" t="n">
-        <v>235000</v>
+        <v>135000</v>
       </c>
       <c r="V99" t="n">
-        <v>127560</v>
+        <v>120040</v>
       </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr">
@@ -13113,28 +13139,28 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr"/>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>11537 Lago De Garda Dr Austin, TX 78747</t>
+          <t>6912 milwood ave apt 106 Canoga park, CA 91303</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>1 (512) 773-6361</t>
+          <t>1 (818) 350-9104</t>
         </is>
       </c>
       <c r="AC99" t="n">
-        <v>8.82</v>
+        <v>4.5</v>
       </c>
       <c r="AD99" t="n">
-        <v>8.82</v>
+        <v>4.5</v>
       </c>
       <c r="AE99" t="n">
-        <v>8.82</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="100">
@@ -13150,12 +13176,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BW-2026-105</t>
+          <t>BW-2026-108</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BW260054</t>
+          <t>BW260057</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -13175,7 +13201,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Adela Maturan</t>
+          <t>Carrie Anne Abella</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -13205,19 +13231,19 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>40×33×39cm(1CTN)</t>
+          <t>36×37×18.5cm(1CTN)</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>0.051 CBM</t>
+          <t>0.025 CBM</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Q100" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
@@ -13230,13 +13256,13 @@
         </is>
       </c>
       <c r="T100" t="n">
-        <v>434240</v>
+        <v>219200</v>
       </c>
       <c r="U100" t="n">
-        <v>260000</v>
+        <v>160000</v>
       </c>
       <c r="V100" t="n">
-        <v>174240</v>
+        <v>59200</v>
       </c>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr">
@@ -13246,28 +13272,28 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr"/>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>3133 Carlos Dr. Dunedin Fl 34698</t>
+          <t>6355 S . Riley St Unit 157  Las Vegas Nevada 89148</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>1 (718) 564-5433</t>
+          <t>16503021232</t>
         </is>
       </c>
       <c r="AC100" t="n">
-        <v>9.380000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AD100" t="n">
-        <v>9.380000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="AE100" t="n">
-        <v>9.380000000000001</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="101">
@@ -13283,12 +13309,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BW-2026-106</t>
+          <t>BW-2026-109</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>BW260055</t>
+          <t>BW260058</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -13308,7 +13334,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Norriemil Pineda</t>
+          <t>Christian M Santos</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -13338,7 +13364,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>36×36×18cm(1CTN)</t>
+          <t>35.5×36×18cm(1CTN)</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -13350,7 +13376,7 @@
         <v>5</v>
       </c>
       <c r="Q101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
@@ -13366,10 +13392,10 @@
         <v>219200</v>
       </c>
       <c r="U101" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="V101" t="n">
-        <v>84200</v>
+        <v>109200</v>
       </c>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr">
@@ -13385,22 +13411,22 @@
       <c r="Z101" t="inlineStr"/>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>31215 Windstone Dr. Winchester CA 92596 USA</t>
+          <t>920 Bentwood Trail, Grand Prairie, Texas, 75052 USA</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>1 (951) 795-8172</t>
+          <t>1 (469) 537-8216</t>
         </is>
       </c>
       <c r="AC101" t="n">
-        <v>4.63</v>
+        <v>2.66</v>
       </c>
       <c r="AD101" t="n">
-        <v>4.63</v>
+        <v>2.66</v>
       </c>
       <c r="AE101" t="n">
-        <v>4.63</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="102">
@@ -13416,12 +13442,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BW-2026-107</t>
+          <t>BW-2026-110</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>BW260056</t>
+          <t>BW260059</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -13441,12 +13467,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Devine Galingan</t>
+          <t>Gohar Yasakhanian</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -13461,7 +13487,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -13471,19 +13497,19 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>26×36×28.5cm(1CTN)</t>
+          <t>50×36×45cm(1CTN)</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0.027 CBM</t>
+          <t>0.081 CBM</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="Q102" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
@@ -13496,13 +13522,13 @@
         </is>
       </c>
       <c r="T102" t="n">
-        <v>255040</v>
+        <v>456800</v>
       </c>
       <c r="U102" t="n">
-        <v>135000</v>
+        <v>376000</v>
       </c>
       <c r="V102" t="n">
-        <v>120040</v>
+        <v>80800</v>
       </c>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
@@ -13512,28 +13538,28 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>이상복</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr"/>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>6912 milwood ave apt 106 Canoga park, CA 91303</t>
+          <t>10571 Horse Creek Ave Shadow Hills CA 91040</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>1 (818) 350-9104</t>
+          <t>1 (818) 667-7794</t>
         </is>
       </c>
       <c r="AC102" t="n">
-        <v>4.5</v>
+        <v>19.1</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.5</v>
+        <v>19.1</v>
       </c>
       <c r="AE102" t="n">
-        <v>4.5</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="103">
@@ -13549,12 +13575,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BW-2026-108</t>
+          <t>BW-2026-111</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>BW260057</t>
+          <t>BW260060</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -13574,12 +13600,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Carrie Anne Abella</t>
+          <t>Laura Swann</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -13594,29 +13620,29 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>5 박스 (CTN)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>36×37×18.5cm(1CTN)</t>
+          <t>49.5×38.5×47.5cm(1CTN) / 55×36×18cm(1CTN) / 49×36.5×22.5cm(3CTN)</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0.025 CBM</t>
+          <t>0.247 CBM</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="Q103" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
@@ -13629,13 +13655,13 @@
         </is>
       </c>
       <c r="T103" t="n">
-        <v>219200</v>
+        <v>1324720</v>
       </c>
       <c r="U103" t="n">
-        <v>160000</v>
+        <v>1090400</v>
       </c>
       <c r="V103" t="n">
-        <v>59200</v>
+        <v>234320</v>
       </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
@@ -13651,22 +13677,22 @@
       <c r="Z103" t="inlineStr"/>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>6355 S . Riley St Unit 157  Las Vegas Nevada 89148</t>
+          <t>"4170 Blackheath Dr Bartlett, TN 38135"</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16503021232</t>
+          <t>(901) 503‑8919</t>
         </is>
       </c>
       <c r="AC103" t="n">
-        <v>5.7</v>
+        <v>57.34</v>
       </c>
       <c r="AD103" t="n">
-        <v>5.7</v>
+        <v>57.34</v>
       </c>
       <c r="AE103" t="n">
-        <v>5.7</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="104">
@@ -13682,12 +13708,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BW-2026-109</t>
+          <t>BW-2026-112</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BW260058</t>
+          <t>BW260061</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -13707,12 +13733,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Christian M Santos</t>
+          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>(주)카스익스프레스</t>
+          <t>유에스퀵</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13727,7 +13753,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>보톡스</t>
+          <t>화장품</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -13737,19 +13763,19 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>35.5×36×18cm(1CTN)</t>
+          <t>54×24×28cm(1CTN)</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0.023 CBM</t>
+          <t>0.036 CBM</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q104" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
@@ -13762,13 +13788,13 @@
         </is>
       </c>
       <c r="T104" t="n">
-        <v>219200</v>
+        <v>182720</v>
       </c>
       <c r="U104" t="n">
-        <v>110000</v>
+        <v>150400</v>
       </c>
       <c r="V104" t="n">
-        <v>109200</v>
+        <v>32320</v>
       </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr">
@@ -13778,28 +13804,28 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr"/>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>920 Bentwood Trail, Grand Prairie, Texas, 75052 USA</t>
+          <t>8620 SAN Gabriel Drive LAREDO, TEXAS 78045</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>1 (469) 537-8216</t>
+          <t>19563493361</t>
         </is>
       </c>
       <c r="AC104" t="n">
-        <v>2.66</v>
+        <v>4.44</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.66</v>
+        <v>4.44</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.66</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="105">
@@ -13810,22 +13836,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BW-2026-110</t>
+          <t>BW-2026-113</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>BW260059</t>
+          <t>BW260062</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>미국</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -13835,17 +13861,17 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>넥서스파마 주식회사</t>
+          <t>텐트러스트</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Gohar Yasakhanian</t>
+          <t>楼 余涛</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>유에스퀵</t>
+          <t>윤세형</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13860,7 +13886,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>화장품</t>
+          <t>특가품목</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -13870,19 +13896,19 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>50×36×45cm(1CTN)</t>
+          <t>49×36×25cm(1CTN)</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0.081 CBM</t>
+          <t>0.044 CBM</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q105" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
@@ -13895,13 +13921,13 @@
         </is>
       </c>
       <c r="T105" t="n">
-        <v>456800</v>
+        <v>240000</v>
       </c>
       <c r="U105" t="n">
-        <v>376000</v>
+        <v>176000</v>
       </c>
       <c r="V105" t="n">
-        <v>80800</v>
+        <v>64000</v>
       </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
@@ -13917,420 +13943,21 @@
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>10571 Horse Creek Ave Shadow Hills CA 91040</t>
+          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>1 (818) 667-7794</t>
+          <t>17589745505</t>
         </is>
       </c>
       <c r="AC105" t="n">
-        <v>19.1</v>
+        <v>7.9</v>
       </c>
       <c r="AD105" t="n">
-        <v>19.1</v>
+        <v>7.9</v>
       </c>
       <c r="AE105" t="n">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>수출 (Export)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>BW-2026-111</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BW260060</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>대한민국 (KOREA)</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>넥서스파마 주식회사</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Laura Swann</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>유에스퀵</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>항공(Air)</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Door To Door</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>화장품</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>5 박스 (CTN)</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>49.5×38.5×47.5cm(1CTN) / 55×36×18cm(1CTN) / 49×36.5×22.5cm(3CTN)</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>0.247 CBM</t>
-        </is>
-      </c>
-      <c r="P106" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>58</v>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T106" t="n">
-        <v>1324720</v>
-      </c>
-      <c r="U106" t="n">
-        <v>1090400</v>
-      </c>
-      <c r="V106" t="n">
-        <v>234320</v>
-      </c>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>"4170 Blackheath Dr Bartlett, TN 38135"</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>(901) 503‑8919</t>
-        </is>
-      </c>
-      <c r="AC106" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>57.34</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>57.34</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>수출 (Export)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>BW-2026-112</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>BW260061</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>미국</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>대한민국 (KOREA)</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>넥서스파마 주식회사</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>MC ALPHA GO/ Alemania Solano de la Torre</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>유에스퀵</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>항공(Air)</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Door To Door</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>화장품</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>1 박스 (CTN)</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>54×24×28cm(1CTN)</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>0.036 CBM</t>
-        </is>
-      </c>
-      <c r="P107" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>8</v>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T107" t="n">
-        <v>182720</v>
-      </c>
-      <c r="U107" t="n">
-        <v>150400</v>
-      </c>
-      <c r="V107" t="n">
-        <v>32320</v>
-      </c>
-      <c r="W107" t="inlineStr"/>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>8620 SAN Gabriel Drive LAREDO, TEXAS 78045</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>19563493361</t>
-        </is>
-      </c>
-      <c r="AC107" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>수출 (Export)</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>BW-2026-113</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BW260062</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>중국</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>대한민국 (KOREA)</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>텐트러스트</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>楼 余涛</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>윤세형</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>항공(Air)</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Door To Door</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>특가품목</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>1 박스 (CTN)</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>49×36×25cm(1CTN)</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>0.044 CBM</t>
-        </is>
-      </c>
-      <c r="P108" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>8</v>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>📦 물류센터 입고 및 접수 완료</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>미수</t>
-        </is>
-      </c>
-      <c r="T108" t="n">
-        <v>240000</v>
-      </c>
-      <c r="U108" t="n">
-        <v>176000</v>
-      </c>
-      <c r="V108" t="n">
-        <v>64000</v>
-      </c>
-      <c r="W108" t="inlineStr"/>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>이상복</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>潍坊市奎文区恒大名都26号楼 余涛</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>17589745505</t>
-        </is>
-      </c>
-      <c r="AC108" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AE108" t="n">
         <v>7.9</v>
       </c>
     </row>

--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -15,7 +15,9 @@
     <sheet name="고객사계정" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="고객화물접수" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="고객수정이력" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="시스템설정" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="매출거래처목록" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="매출거래처요율" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="시스템설정" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AE106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4023,16 +4025,8 @@
           <t>{"client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장잔액"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": []}</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
@@ -13959,6 +13953,835 @@
       </c>
       <c r="AE105" t="n">
         <v>7.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>BW-2026-114</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BW260063</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>GMV SUPPLIES</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>2</v>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T106" t="n">
+        <v>45680</v>
+      </c>
+      <c r="U106" t="n">
+        <v>37600</v>
+      </c>
+      <c r="V106" t="n">
+        <v>8080</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>10145 VIA DE LA AMISTAD STE 10 &amp; 11, SAN DIEGO CA. 92154, USA</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>16461388599</t>
+        </is>
+      </c>
+      <c r="AC106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>국가</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>운송형태</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>품명</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기본중량</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기본요금</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>추가단가</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>1CBM당단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G3" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>일반화물</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3700000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>75840</v>
+      </c>
+      <c r="G5" t="n">
+        <v>35840</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>22840</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22840</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>75840</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35840</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>보톡스 필러</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>35000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>주식회사 케이티글로발</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G10" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G11" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>텐트러스트</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>특가품목</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>텐트러스트</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>특가품목</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>30840</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30840</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>맥익스프레스 인터내셔날(주)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>42000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>맥익스프레스 인터내셔날(주)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>리턴의원</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>보톡스 필러 (Botox &amp; Filler)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3700000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>뷰메디스</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G17" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>뷰메디스</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>필러</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39840</v>
+      </c>
+      <c r="G18" t="n">
+        <v>39840</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>해상(LCL)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8500</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SYSTEM_META</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "", "주소": ""}, "주식회사 조은로직스": {"사업자등록번호": "", "이메일": "", "담당자": "조정희 과장", "전화번호": "", "주소": ""}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "", "담당자": "히엔/이동렬", "전화번호": "", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "주식회사 케이티글로발": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "", "담당자": "박수진", "전화번호": "", "주소": ""}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "리턴의원": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "뷰메디스": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}, "유에스퀵": {"사업자등록번호": "", "이메일": "", "담당자": "", "전화번호": "", "주소": ""}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원", "지급상태": "미지급"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -15560,22 +16383,212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>SYSTEM_META</t>
+          <t>거래처명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>이메일</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>담당자</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>전화번호</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>주소</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"backup_version": 2, "client_list": ["아코글로벌", "주식회사 조은로직스", "넥서스파마 주식회사", "(주)카스익스프레스", "주식회사 케이티글로발", "글로우필메디앤코", "텐트러스트", "맥익스프레스 인터내셔날(주)", "리턴의원", "뷰메디스", "유에스퀵"], "client_rates": {"아코글로벌": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "주식회사 조은로직스": {"미국": {"항공(Air)": {"일반화물": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "넥서스파마 주식회사": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}, "화장품": {"기본중량": 1.0, "기본요금": 22840, "추가단가": 22840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 75840, "추가단가": 35840, "1CBM당단가": 0}}}}, "(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스 필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "주식회사 케이티글로발": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 0}}}}, "글로우필메디앤코": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "텐트러스트": {"중국": {"해상(LCL)": {"특가품목": {"기본중량": 1.0, "기본요금": 30000, "추가단가": 30000, "1CBM당단가": 0}}}, "미국": {"항공(Air)": {"특가품목": {"기본중량": 1.0, "기본요금": 30840, "추가단가": 30840, "1CBM당단가": 0}}}}, "맥익스프레스 인터내셔날(주)": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 42000, "추가단가": 42000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 45000, "추가단가": 45000, "1CBM당단가": 0}}}}, "리턴의원": {"미국": {"항공(Air)": {"보톡스 필러 (Botox &amp; Filler)": {"기본중량": 1.0, "기본요금": 38000, "추가단가": 25000, "1CBM당단가": 3700000}}}}, "뷰메디스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39840, "추가단가": 39840, "1CBM당단가": 0}}}}, "유에스퀵": {"중국": {"해상(LCL)": {"화장품": {"기본중량": 1.0, "기본요금": 8500, "추가단가": 8500, "1CBM당단가": 0}}}}}, "client_infos": {"아코글로벌": {"사업자등록번호": "778-09-03229", "이메일": "infoakoglobal@gmail.com", "담당자": "박장우대표님", "전화번호": "nan", "주소": "nan"}, "주식회사 조은로직스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "조정희 과장", "전화번호": "nan", "주소": "nan"}, "넥서스파마 주식회사": {"사업자등록번호": "199-87-00524", "이메일": "nan", "담당자": "히엔/이동렬", "전화번호": "nan", "주소": "서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)"}, "(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "주식회사 케이티글로발": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}, "글로우필메디앤코": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "텐트러스트": {"사업자등록번호": "646-13-01784", "이메일": "nan", "담당자": "박수진", "전화번호": "nan", "주소": "nan"}, "맥익스프레스 인터내셔날(주)": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "리턴의원": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "뷰메디스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}}, "supplier_list": ["(주)카스익스프레스", "유에스퀵", "윤세형", "bf t"], "supplier_rates": {"(주)카스익스프레스": {"미국": {"항공(Air)": {"보톡스": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 35000, "추가단가": 25000, "1CBM당단가": 0}}}}, "유에스퀵": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 18800, "추가단가": 18800, "1CBM당단가": 0}}}}, "윤세형": {"중국": {"해상(LCL)": {"보톡스": {"기본중량": 1.0, "기본요금": 34000, "추가단가": 34000, "1CBM당단가": 0}, "필러": {"기본중량": 1.0, "기본요금": 39000, "추가단가": 39000, "1CBM당단가": 0}, "특가품목": {"기본중량": 1.0, "기본요금": 0, "추가단가": 0, "1CBM당단가": 3700000}}}}, "bf t": {"미국": {"항공(Air)": {"화장품": {"기본중량": 1.0, "기본요금": 15530, "추가단가": 15530, "1CBM당단가": 0}}}}}, "supplier_infos": {"(주)카스익스프레스": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "nan"}, "유에스퀵": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "심사면", "전화번호": "nan", "주소": "nan"}, "윤세형": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "윤세형", "전화번호": "nan", "주소": "nan"}, "bf t": {"사업자등록번호": "nan", "이메일": "nan", "담당자": "nan", "전화번호": "nan", "주소": "고촌"}}, "ledger_data": [{"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "1365000", "금액(원)": 1316250, "적요": "통장잔액 법인통장", "지급상태": "지급완료"}, {"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 70000, "적요": "5710", "지급상태": "지급완료"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 70000, "적요": "아코 박수진 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈 저녁식대", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 인천 용달비", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥서스 파마 고촌 용달입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "필러 20박스 윤세형 입고비용", "지급상태": "지급완료"}, {"날짜": "2026-10-20", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "BFT 점심식사", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "회사 - 인천 시노트랜스(맥인스프레스 30박스)", "지급상태": "미지급"}, {"날짜": "2026-10-21", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 81000, "적요": "회식비", "지급상태": "미지급"}, {"날짜": "2026-10-22", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 135900, "적요": "1차 조철희 선배 필러 200박스 미팅  93000원2차 조철희 led건미팅 42900원", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109900, "적요": "탑 이동훈 이사 저녁식대", "지급상태": "미지급"}, {"날짜": "2026-10-23", "구분": "지출 (-)", "항목": "주유비(차량유지비)", "금액(원)": 125000, "적요": "엔진오일 교환비용 5710", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 26000, "적요": "5710 대리비용 ", "지급상태": "미지급"}, {"날짜": "2026-10-27", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 109000, "적요": "에이블쿠 인터내셔날 2명 83000원 대리비 26000원", "지급상태": "미지급"}, {"날짜": "2026-10-29", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 50000, "적요": "필러 20박스 리턴건 선불비용지불 -50000원 가지급건으로처리", "지급상태": "미지급"}, {"날짜": "2026-10-30", "구분": "지출 (-)", "지급상태": "미지급", "항목": "접대비", "금액(원)": 120000, "적요": "양공열 식사 90000만원 대리비용30000원"}], "expense_data": [{"날짜": "2026-10-02", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 68000, "적요": "남양김태호 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-03", "구분": "지출 (-)", "항목": "주유비 (차량유지비)", "금액(원)": 70000, "적요": "주유비 5710", "작성자": "이상복"}, {"날짜": "2026-10-12", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 90000, "적요": "아코 박수진 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-13", "구분": "지출 (-)", "항목": "접대비", "금액(원)": 176000, "적요": "맥 이지훈팀장 저녁식대", "작성자": "이상복"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "리턴의원 용달비(회사-인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 25000, "적요": "넥세스파마 용달비(회사-K-GLOBAL)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "지출 (-)", "항목": "기타 잡비", "금액(원)": 35000, "적요": "신규업체 20박스 용달비(회사 - 인천)", "작성자": "정해균"}, {"날짜": "2026-10-19", "구분": "수입 (+)", "항목": "기타 영업수입", "금액(원)": 1365000, "적요": "통장 잔액", "작성자": "이상복"}], "meeting_data": [], "note_data": [], "customer_accounts": [{"아이디": "joeun", "비밀번호해시": "335f13ccec68fcb9de22e60226df2c64b192ca4440dfa503795714ce6d0730e3", "고객사상호": "주식회사 조은로직스", "담당자연락처": "조철희", "상태": "승인", "생성일시": "2026-10-24 03:34:34"}], "customer_requests": [{"접수번호": "REQ-A458BDB2B3", "접수일시": "2026-10-24 03:53:51", "고객사아이디": "joeun", "고객사상호": "주식회사 조은로직스", "화주상호": "주식회사 조은로직스", "화주주소": "112", "화주전화번호": "2112", "해외수하인": "1212", "해외수하인주소": "121", "해외수하인전화번호": "121", "도착국가": "미국", "품목": "보톡스", "운송형태": "항공(Air)", "실제중량kg": "10.00", "가로cm": "25.50", "세로cm": "35.00", "높이cm": "10.00", "박스수량": "1", "CBM": "0.0089", "부피중량kg": "1.78", "추가요청": "", "상태": "B/L 등록", "연결 B/L 번호": "BW260027", "변경요청JSON": "", "관리자메모": "", "승인일시": "2026-10-24 04:13:29", "승인자": "lsb", "B/L등록일시": "2026-10-24 04:28:57"}], "customer_history": [{"일시": "2026-10-24 03:53:51", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "신규 접수", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:58:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 03:59:02", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "주식회사 조은로직스", "작업": "B/L 등록 전 고객 수정", "변경내용": "{\"접수번호\": \"REQ-A458BDB2B3\", \"접수일시\": \"2026-10-24 03:53:51\", \"고객사아이디\": \"joeun\", \"고객사상호\": \"주식회사 조은로직스\", \"화주상호\": \"주식회사 조은로직스\", \"화주주소\": \"112\", \"화주전화번호\": \"2112\", \"해외수하인\": \"1212\", \"해외수하인주소\": \"121\", \"해외수하인전화번호\": \"121\", \"도착국가\": \"미국\", \"품목\": \"보톡스\", \"운송형태\": \"항공(Air)\", \"실제중량kg\": \"10.00\", \"가로cm\": \"25.50\", \"세로cm\": \"35.00\", \"높이cm\": \"10.00\", \"박스수량\": \"1\", \"CBM\": \"0.0089\", \"부피중량kg\": \"1.78\", \"추가요청\": \"\", \"상태\": \"접수\", \"연결 B/L 번호\": \"\", \"변경요청JSON\": \"\", \"관리자메모\": \"\"}"}, {"일시": "2026-10-24 04:00:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:01:58", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": ""}, {"일시": "2026-10-24 04:13:29", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "고객 화물 승인 및 B/L 번호 자동 발급", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:14:06", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:20:43", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 연결 상태 변경", "변경내용": "BW260027"}, {"일시": "2026-10-24 04:28:57", "접수번호": "REQ-A458BDB2B3", "고객사아이디": "joeun", "작업자": "lsb", "작업": "B/L 번호 연결 및 수출입 B/L 저장", "변경내용": "BW260027"}]}</t>
-        </is>
-      </c>
+          <t>아코글로벌</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>778-09-03229</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>infoakoglobal@gmail.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>박장우대표님</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>주식회사 조은로직스</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>조정희 과장</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>199-87-00524</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>히엔/이동렬</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>서울특별시 강서구 공항대로45길 71,6층(등촌동.씨에이치빌딩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>주식회사 케이티글로발</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>고촌</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>글로우필메디앤코</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>텐트러스트</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>646-13-01784</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>박수진</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>맥익스프레스 인터내셔날(주)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>리턴의원</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>뷰메디스</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-30.xlsx
@@ -13963,7 +13963,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr"/>
